--- a/data/b2_candoi/B2 Candói 01-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 01-2026.xlsx
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1869.57</v>
+        <v>1951.64</v>
       </c>
     </row>
     <row r="3">
@@ -4828,61 +4828,61 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57433.85</v>
+        <v>57948.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1738.66</v>
+        <v>1441.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2041.84</v>
+        <v>1182.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1459.68</v>
+        <v>2490.76</v>
       </c>
     </row>
     <row r="7">
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3386.27</v>
+        <v>3350.6</v>
       </c>
     </row>
     <row r="9">
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>996.4400000000001</v>
+        <v>1035.08</v>
       </c>
     </row>
     <row r="10">
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>8944.91</v>
+        <v>9454.74</v>
       </c>
     </row>
     <row r="11">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>920.84</v>
+        <v>979.96</v>
       </c>
     </row>
     <row r="12">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3483.66</v>
+        <v>3301.57</v>
       </c>
     </row>
     <row r="13">
@@ -5008,12 +5008,12 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>19954.97</v>
+        <v>20456.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -5022,29 +5022,29 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1695.5</v>
+        <v>1460.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46047</v>
+        <v>46044</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>6930</v>
+        <v>3094.59</v>
       </c>
     </row>
     <row r="16">
@@ -5053,16 +5053,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1404.9</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="17">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3383.47</v>
+        <v>3279.74</v>
       </c>
     </row>
     <row r="18">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2991.67</v>
+        <v>3137.11</v>
       </c>
     </row>
   </sheetData>
